--- a/data/pupil/3_processed/15_semantic_similarity/event/sub_1036_cosine_similarity.xlsx
+++ b/data/pupil/3_processed/15_semantic_similarity/event/sub_1036_cosine_similarity.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,20 +436,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Pool Party</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Sea Ice</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Natalie Wood</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Grandfather Clocks</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Impatient Billionaire</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Dont Look</t>
         </is>
@@ -460,15 +470,21 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
         <v>0.5273391604423523</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>0.4288378357887268</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
         <v>0.3868356645107269</v>
       </c>
     </row>
@@ -480,12 +496,18 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
         <v>0.2628746926784515</v>
       </c>
-      <c r="D3" t="n">
-        <v>0</v>
-      </c>
       <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
         <v>0.216803640127182</v>
       </c>
     </row>
@@ -497,12 +519,18 @@
         <v>0</v>
       </c>
       <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
         <v>0.2779047191143036</v>
       </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
       <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -514,12 +542,18 @@
         <v>0</v>
       </c>
       <c r="C5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" t="n">
         <v>0.4308476746082306</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.4507337212562561</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -531,12 +565,18 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="n">
         <v>0.5107572078704834</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.3066078722476959</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
         <v>0.3738964796066284</v>
       </c>
     </row>
@@ -554,6 +594,12 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
         <v>0.4389572739601135</v>
       </c>
     </row>
@@ -568,9 +614,15 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
         <v>0.4195172488689423</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.5260348916053772</v>
       </c>
     </row>
@@ -582,12 +634,18 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>0.5582032799720764</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -596,15 +654,21 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" t="n">
         <v>0.5130457878112793</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -613,15 +677,21 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" t="n">
         <v>0.4429910778999329</v>
       </c>
-      <c r="C11" t="n">
-        <v>0</v>
-      </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -641,6 +711,12 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -658,6 +734,12 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -673,6 +755,12 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
         <v>-0.07750085741281509</v>
       </c>
     </row>
@@ -684,12 +772,18 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
         <v>0.4430982172489166</v>
       </c>
-      <c r="D15" t="n">
-        <v>0</v>
-      </c>
       <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
         <v>0.1563834995031357</v>
       </c>
     </row>
@@ -707,6 +801,12 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
         <v>0.08909141272306442</v>
       </c>
     </row>
@@ -724,6 +824,12 @@
         <v>0</v>
       </c>
       <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.3869626522064209</v>
       </c>
     </row>
@@ -741,6 +847,12 @@
         <v>0</v>
       </c>
       <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.5467873811721802</v>
       </c>
     </row>
@@ -760,6 +872,10 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -777,6 +893,10 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -794,14 +914,16 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
+      <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
         <v>0</v>
       </c>
@@ -809,6 +931,10 @@
         <v>0</v>
       </c>
       <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -816,16 +942,18 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
+      <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" t="n">
         <v>0.5663295388221741</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0.4025516211986542</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
         <v>0.16648069024086</v>
       </c>
     </row>
@@ -833,16 +961,18 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" t="n">
         <v>0.2870035171508789</v>
       </c>
-      <c r="D24" t="n">
-        <v>0</v>
-      </c>
       <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -851,13 +981,15 @@
         <v>24</v>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="n">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="n">
         <v>0.4216700196266174</v>
       </c>
-      <c r="D25" t="n">
-        <v>0</v>
-      </c>
       <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
         <v>0.3343805968761444</v>
       </c>
     </row>
@@ -866,13 +998,15 @@
         <v>25</v>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="n">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="n">
         <v>0.4766649603843689</v>
       </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
       <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="n">
         <v>0.334498256444931</v>
       </c>
     </row>
@@ -881,13 +1015,15 @@
         <v>26</v>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>0</v>
-      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
         <v>0</v>
       </c>
       <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="n">
         <v>0.5150554776191711</v>
       </c>
     </row>
@@ -896,13 +1032,15 @@
         <v>27</v>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="n">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="n">
         <v>0.2807149291038513</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.2460001707077026</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -911,13 +1049,15 @@
         <v>28</v>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="n">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="n">
         <v>0.5033411979675293</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.3691468238830566</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
         <v>0.1481826156377792</v>
       </c>
     </row>
@@ -926,13 +1066,15 @@
         <v>29</v>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="n">
-        <v>0</v>
-      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
         <v>0.3893732726573944</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -941,11 +1083,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="n">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -954,11 +1098,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="n">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -967,11 +1113,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="n">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="n">
         <v>0.5090303421020508</v>
       </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="n">
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="n">
         <v>0.8061495423316956</v>
       </c>
     </row>
@@ -980,11 +1128,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="n">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="n">
         <v>0.717786967754364</v>
       </c>
     </row>
@@ -993,11 +1143,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="n">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="n">
         <v>0.8019677400588989</v>
       </c>
     </row>
@@ -1006,11 +1158,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="n">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="n">
         <v>0.4710340201854706</v>
       </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
         <v>0.5711533427238464</v>
       </c>
     </row>
@@ -1019,11 +1173,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="n">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="n">
         <v>0.2815088629722595</v>
       </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="n">
         <v>0.3856030702590942</v>
       </c>
     </row>
@@ -1032,11 +1188,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="n">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1045,11 +1203,13 @@
         <v>38</v>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="n">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="n">
         <v>0.2365564554929733</v>
       </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="n">
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="n">
         <v>0.4379169940948486</v>
       </c>
     </row>
@@ -1058,11 +1218,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="n">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="n">
         <v>0.3829468488693237</v>
       </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="n">
         <v>0.4813437461853027</v>
       </c>
     </row>
@@ -1071,11 +1233,13 @@
         <v>40</v>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="n">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="n">
         <v>0.2795731127262115</v>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="n">
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
         <v>0.3680088818073273</v>
       </c>
     </row>
@@ -1084,11 +1248,13 @@
         <v>41</v>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="n">
         <v>-0.06588736176490784</v>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="n">
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="n">
         <v>0.2443611472845078</v>
       </c>
     </row>
@@ -1097,154 +1263,182 @@
         <v>42</v>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
       <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
         <v>43</v>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
       <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
         <v>44</v>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="n">
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="n">
         <v>0.2705381214618683</v>
       </c>
-      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
         <v>45</v>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="n">
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="n">
         <v>0.3743953108787537</v>
       </c>
-      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
         <v>46</v>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
         <v>47</v>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="n">
         <v>0.6144179701805115</v>
       </c>
-      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
         <v>48</v>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="n">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="n">
         <v>0.5334351062774658</v>
       </c>
-      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
         <v>49</v>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="n">
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="n">
         <v>0.3611153364181519</v>
       </c>
-      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
         <v>50</v>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
         <v>51</v>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
         <v>52</v>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="n">
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="n">
         <v>0.4592687487602234</v>
       </c>
-      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
         <v>53</v>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
         <v>54</v>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="n">
         <v>0.3551807105541229</v>
       </c>
-      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
         <v>55</v>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
       <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
